--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16891272</v>
+        <v>16891965</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>1506</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>3500 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591161.9640713367</v>
+        <v>591281</v>
       </c>
       <c r="R2" t="n">
-        <v>7099534.89453371</v>
+        <v>7099785</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2014-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,516 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16891479</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3500 m OSO Granåsen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>591268</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7099396</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16891490</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3400 m Ö Granåsen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591211</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7099657</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16891921</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3400 m Ö Granåsen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7099674</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16892197</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3400 m Ö Granåsen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591217</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7099675</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16891272</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3400 m Ö Granåsen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>591162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7099535</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017526</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891965</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017475</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891479</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891490</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017553</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017554</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017555</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017556</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017557</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017558</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017559</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017560</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017561</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017562</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2319,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017563</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2336,6 +2421,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017564</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017565</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2540,6 +2635,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891921</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,6 +2737,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017514</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2739,6 +2844,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16892197</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2836,6 +2946,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017501</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16891272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3036,6 +3156,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017566</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3133,6 +3258,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017569</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3230,6 +3360,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017570</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017572</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3424,6 +3564,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017518</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3521,6 +3666,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017498</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3618,6 +3768,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017499</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3715,6 +3870,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017511</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3812,6 +3972,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017508</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3909,6 +4074,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017509</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4006,6 +4176,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017510</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4103,6 +4278,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017512</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4200,6 +4380,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017522</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4297,8 +4482,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135017526</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135017475</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135017553</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>135017554</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135017555</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135017556</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135017557</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135017558</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135017559</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>135017560</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135017561</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135017562</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135017563</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>135017564</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135017565</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135017514</v>
       </c>
       <c r="B21" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>135017501</v>
       </c>
       <c r="B23" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135017566</v>
       </c>
       <c r="B25" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135017569</v>
       </c>
       <c r="B26" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>135017570</v>
       </c>
       <c r="B27" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135017572</v>
       </c>
       <c r="B28" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135017518</v>
       </c>
       <c r="B29" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135017498</v>
       </c>
       <c r="B30" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135017499</v>
       </c>
       <c r="B31" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135017511</v>
       </c>
       <c r="B32" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>135017508</v>
       </c>
       <c r="B33" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>135017509</v>
       </c>
       <c r="B34" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135017510</v>
       </c>
       <c r="B35" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>135017512</v>
       </c>
       <c r="B36" t="n">
-        <v>98277</v>
+        <v>98321</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>135017522</v>
       </c>
       <c r="B37" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>135017523</v>
       </c>
       <c r="B38" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135017526</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>135017475</v>
       </c>
       <c r="B4" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>135017553</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>135017554</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>135017555</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135017556</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135017557</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135017558</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135017559</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>135017560</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>135017561</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135017562</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>135017563</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>135017564</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>135017565</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>135017514</v>
       </c>
       <c r="B21" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>135017501</v>
       </c>
       <c r="B23" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>135017566</v>
       </c>
       <c r="B25" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135017569</v>
       </c>
       <c r="B26" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>135017570</v>
       </c>
       <c r="B27" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135017572</v>
       </c>
       <c r="B28" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135017518</v>
       </c>
       <c r="B29" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135017498</v>
       </c>
       <c r="B30" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135017499</v>
       </c>
       <c r="B31" t="n">
-        <v>109980</v>
+        <v>110007</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>135017511</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>135017508</v>
       </c>
       <c r="B33" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v>135017509</v>
       </c>
       <c r="B34" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135017510</v>
       </c>
       <c r="B35" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>135017512</v>
       </c>
       <c r="B36" t="n">
-        <v>98321</v>
+        <v>98348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>135017522</v>
       </c>
       <c r="B37" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>135017523</v>
       </c>
       <c r="B38" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2745,48 +2745,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16892197</v>
+        <v>136487005</v>
       </c>
       <c r="B22" t="n">
-        <v>80461</v>
+        <v>80588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Flakaberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>591217</v>
+        <v>590966</v>
       </c>
       <c r="R22" t="n">
-        <v>7099675</v>
+        <v>7099401</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2810,17 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2835,27 +2830,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16892197</t>
+          <t>https://artportalen.se/Sighting/136487005</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135017501</v>
+        <v>16892197</v>
       </c>
       <c r="B23" t="n">
-        <v>80558</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,17 +2878,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>591153</v>
+        <v>591217</v>
       </c>
       <c r="R23" t="n">
-        <v>7099534</v>
+        <v>7099675</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2917,12 +2912,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2937,27 +2937,27 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017501</t>
+          <t>https://artportalen.se/Sighting/16892197</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16891272</v>
+        <v>135017501</v>
       </c>
       <c r="B24" t="n">
-        <v>80467</v>
+        <v>80558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2965,37 +2965,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3400 m Ö Granåsen, Ås lm</t>
+          <t>Vallsjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>591162</v>
+        <v>591153</v>
       </c>
       <c r="R24" t="n">
-        <v>7099535</v>
+        <v>7099534</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3019,17 +3019,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Sveaskog naturvärdesinventering</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3044,27 +3039,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16891272</t>
+          <t>https://artportalen.se/Sighting/135017501</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135017566</v>
+        <v>16891272</v>
       </c>
       <c r="B25" t="n">
-        <v>99186</v>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3072,37 +3067,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vallsjöberget, Ås lm</t>
+          <t>3400 m Ö Granåsen, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>591274</v>
+        <v>591162</v>
       </c>
       <c r="R25" t="n">
-        <v>7099457</v>
+        <v>7099535</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3126,12 +3121,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Sveaskog naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3140,31 +3140,30 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017566</t>
+          <t>https://artportalen.se/Sighting/16891272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135017569</v>
+        <v>135017566</v>
       </c>
       <c r="B26" t="n">
         <v>99186</v>
@@ -3199,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>591148</v>
+        <v>591274</v>
       </c>
       <c r="R26" t="n">
-        <v>7099523</v>
+        <v>7099457</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3243,6 +3242,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3260,13 +3260,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017569</t>
+          <t>https://artportalen.se/Sighting/135017566</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135017570</v>
+        <v>135017569</v>
       </c>
       <c r="B27" t="n">
         <v>99186</v>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>591178</v>
+        <v>591148</v>
       </c>
       <c r="R27" t="n">
-        <v>7099537</v>
+        <v>7099523</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3362,16 +3362,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017570</t>
+          <t>https://artportalen.se/Sighting/135017569</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135017572</v>
+        <v>135017570</v>
       </c>
       <c r="B28" t="n">
-        <v>98290</v>
+        <v>99186</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219815</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>591268</v>
+        <v>591178</v>
       </c>
       <c r="R28" t="n">
-        <v>7099456</v>
+        <v>7099537</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3464,16 +3464,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017572</t>
+          <t>https://artportalen.se/Sighting/135017570</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135017518</v>
+        <v>135017572</v>
       </c>
       <c r="B29" t="n">
-        <v>111237</v>
+        <v>98290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220240</v>
+        <v>219815</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>591204</v>
+        <v>591268</v>
       </c>
       <c r="R29" t="n">
-        <v>7099540</v>
+        <v>7099456</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3566,16 +3566,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017518</t>
+          <t>https://artportalen.se/Sighting/135017572</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135017498</v>
+        <v>135017518</v>
       </c>
       <c r="B30" t="n">
-        <v>110007</v>
+        <v>111237</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3583,21 +3583,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221184</v>
+        <v>220240</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>591238</v>
+        <v>591204</v>
       </c>
       <c r="R30" t="n">
-        <v>7099483</v>
+        <v>7099540</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3668,13 +3668,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017498</t>
+          <t>https://artportalen.se/Sighting/135017518</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135017499</v>
+        <v>135017498</v>
       </c>
       <c r="B31" t="n">
         <v>110007</v>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>591279</v>
+        <v>591238</v>
       </c>
       <c r="R31" t="n">
-        <v>7099455</v>
+        <v>7099483</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3770,16 +3770,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017499</t>
+          <t>https://artportalen.se/Sighting/135017498</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135017511</v>
+        <v>135017499</v>
       </c>
       <c r="B32" t="n">
-        <v>98131</v>
+        <v>110007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3787,21 +3787,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>221184</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>591204</v>
+        <v>591279</v>
       </c>
       <c r="R32" t="n">
-        <v>7099540</v>
+        <v>7099455</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3872,16 +3872,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017511</t>
+          <t>https://artportalen.se/Sighting/135017499</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135017508</v>
+        <v>135017511</v>
       </c>
       <c r="B33" t="n">
-        <v>99291</v>
+        <v>98131</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3889,21 +3889,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3913,10 +3913,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>591115</v>
+        <v>591204</v>
       </c>
       <c r="R33" t="n">
-        <v>7099452</v>
+        <v>7099540</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3974,13 +3974,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017508</t>
+          <t>https://artportalen.se/Sighting/135017511</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135017509</v>
+        <v>135017508</v>
       </c>
       <c r="B34" t="n">
         <v>99291</v>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>591110</v>
+        <v>591115</v>
       </c>
       <c r="R34" t="n">
-        <v>7099504</v>
+        <v>7099452</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4076,13 +4076,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017509</t>
+          <t>https://artportalen.se/Sighting/135017508</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135017510</v>
+        <v>135017509</v>
       </c>
       <c r="B35" t="n">
         <v>99291</v>
@@ -4117,10 +4117,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>591144</v>
+        <v>591110</v>
       </c>
       <c r="R35" t="n">
-        <v>7099533</v>
+        <v>7099504</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4178,16 +4178,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017510</t>
+          <t>https://artportalen.se/Sighting/135017509</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135017512</v>
+        <v>135017510</v>
       </c>
       <c r="B36" t="n">
-        <v>98348</v>
+        <v>99291</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222736</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Majbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Athyrium filix-femina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>591190</v>
+        <v>591144</v>
       </c>
       <c r="R36" t="n">
-        <v>7099540</v>
+        <v>7099533</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4280,16 +4280,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017512</t>
+          <t>https://artportalen.se/Sighting/135017510</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135017522</v>
+        <v>135017512</v>
       </c>
       <c r="B37" t="n">
-        <v>98320</v>
+        <v>98348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4297,21 +4297,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>222736</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Majbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Athyrium filix-femina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4321,10 +4321,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>591239</v>
+        <v>591190</v>
       </c>
       <c r="R37" t="n">
-        <v>7099484</v>
+        <v>7099540</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4382,13 +4382,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135017522</t>
+          <t>https://artportalen.se/Sighting/135017512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135017523</v>
+        <v>135017522</v>
       </c>
       <c r="B38" t="n">
         <v>98320</v>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>591280</v>
+        <v>591239</v>
       </c>
       <c r="R38" t="n">
-        <v>7099457</v>
+        <v>7099484</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4483,6 +4483,108 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135017522</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135017523</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98320</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>591280</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7099457</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135017523</t>
         </is>
@@ -4527,6 +4629,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28716-2023 artfynd.xlsx
+++ b/artfynd/A 28716-2023 artfynd.xlsx
@@ -2748,7 +2748,7 @@
         <v>136487005</v>
       </c>
       <c r="B22" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
